--- a/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
+++ b/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_CS1_Echo_Demo\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46396D2-F6C1-4DA8-AF41-AF8EECADC2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D77F5E-5D07-4F32-94A0-4381AEE0D94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>색좌표(목표)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>mA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>curr max lvl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pwm max</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -186,7 +198,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -209,6 +221,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -218,7 +256,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -244,6 +282,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -587,182 +637,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7E6260-E2E5-489C-A08B-CAF06F81E7A4}">
-  <dimension ref="B2:L13"/>
+  <dimension ref="B2:L14"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="5.8125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="8.5625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="5.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3">
-        <v>13.17</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3">
+        <v>22.3</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B4" s="4" t="s">
+      <c r="F4" s="3">
+        <v>2418</v>
+      </c>
+      <c r="G4" s="12">
+        <f>D4*F4/4095</f>
+        <v>13.167619047619048</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3">
-        <v>11.5</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C5" s="3">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B5" s="5" t="s">
+      <c r="F5" s="3">
+        <v>3413</v>
+      </c>
+      <c r="G5" s="12">
+        <f>D5*F5/4095</f>
+        <v>11.501684981684981</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3">
-        <v>6.08</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6.24</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B7" s="8" t="s">
+      <c r="F6" s="3">
+        <v>3990</v>
+      </c>
+      <c r="G6" s="12">
+        <f>D6*F6/4095</f>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
+      <c r="C8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8" t="s">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8" t="s">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B8" s="8"/>
-      <c r="C8" s="3" t="s">
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B9" s="9"/>
+      <c r="C9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C10" s="3">
         <v>0.71519999999999995</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D10" s="3">
         <v>0.28549999999999998</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E10" s="3">
         <v>255</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <f>$C$3*E9/255</f>
-        <v>13.17</v>
-      </c>
-      <c r="I9" s="7">
-        <f>$C$4*F9/255</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
-        <f>$C$5*G9/255</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.1802</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.72729999999999995</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
       <c r="F10" s="3">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" ref="H10:H12" si="0">$C$3*E10/255</f>
-        <v>0</v>
+        <f>$G$4*E10/255</f>
+        <v>13.167619047619048</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" ref="I10:I13" si="1">$C$4*F10/255</f>
-        <v>11.5</v>
+        <f>$G$5*F10/255</f>
+        <v>0</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" ref="J10:J13" si="2">$C$5*G10/255</f>
+        <f>$G$6*G10/255</f>
         <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
@@ -773,35 +838,35 @@
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B11" s="5" t="s">
-        <v>5</v>
+      <c r="B11" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C11" s="3">
-        <v>0.14710000000000001</v>
+        <v>0.1802</v>
       </c>
       <c r="D11" s="3">
-        <v>5.7599999999999998E-2</v>
+        <v>0.72729999999999995</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="G11" s="3">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="0"/>
+        <f>$G$4*E11/255</f>
         <v>0</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>$G$5*F11/255</f>
+        <v>11.501684981684981</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="2"/>
-        <v>6.08</v>
+        <f>$G$6*G11/255</f>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>11</v>
@@ -811,89 +876,128 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>255</v>
+      </c>
+      <c r="H12" s="7">
+        <f>$G$4*E12/255</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <f>$G$5*F12/255</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="7">
+        <f>$G$6*G12/255</f>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C13" s="3">
         <v>0.312</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E13" s="3">
         <v>255</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F13" s="3">
         <v>255</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G13" s="3">
         <v>213</v>
       </c>
-      <c r="H12" s="7">
-        <f t="shared" si="0"/>
-        <v>13.17</v>
-      </c>
-      <c r="I12" s="7">
-        <f t="shared" si="1"/>
-        <v>11.5</v>
-      </c>
-      <c r="J12" s="7">
-        <f t="shared" si="2"/>
-        <v>5.0785882352941174</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="H13" s="7">
+        <f>$G$4*E13/255</f>
+        <v>13.167619047619048</v>
+      </c>
+      <c r="I13" s="7">
+        <f>$G$5*F13/255</f>
+        <v>11.501684981684981</v>
+      </c>
+      <c r="J13" s="7">
+        <f>$G$6*G13/255</f>
+        <v>5.0785882352941183</v>
+      </c>
+      <c r="K13" s="3">
         <v>0.317</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L13" s="3">
         <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B13" s="6" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.6">
+      <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C14" s="3">
         <v>0.16400000000000001</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D14" s="3">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E14" s="3">
         <v>15</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F14" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G14" s="3">
         <v>255</v>
       </c>
-      <c r="H13" s="7">
-        <f>$C$3*E13/255</f>
-        <v>0.77470588235294124</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="1"/>
-        <v>9.0196078431372548E-2</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="2"/>
-        <v>6.08</v>
-      </c>
-      <c r="K13" s="3">
+      <c r="H14" s="7">
+        <f>$G$4*E14/255</f>
+        <v>0.77456582633053228</v>
+      </c>
+      <c r="I14" s="7">
+        <f>$G$5*F14/255</f>
+        <v>9.0209293973999849E-2</v>
+      </c>
+      <c r="J14" s="7">
+        <f>$G$6*G14/255</f>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="K14" s="3">
         <v>0.16600000000000001</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L14" s="3">
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="H7:J7"/>
+  <mergeCells count="7">
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
+++ b/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_CS1_Echo_Demo\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D77F5E-5D07-4F32-94A0-4381AEE0D94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4CB220-F0E2-4A11-A8AB-3E1971178C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
+    <workbookView xWindow="43080" yWindow="5760" windowWidth="29040" windowHeight="15720" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t>색좌표(목표)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -107,6 +107,25 @@
   </si>
   <si>
     <t>pwm max</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mA</t>
+  </si>
+  <si>
+    <t>LED 최대 전류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>색좌표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력 계조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPT 계산</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -198,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -247,6 +266,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -256,7 +286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -284,16 +314,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -637,41 +670,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7E6260-E2E5-489C-A08B-CAF06F81E7A4}">
-  <dimension ref="B2:L14"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.6"/>
+  <dimension ref="B2:T14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="8.5625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="5.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="8.58203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="12"/>
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
+      <c r="N3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="12"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
@@ -687,15 +725,24 @@
       <c r="F4" s="3">
         <v>2418</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="9">
         <f>D4*F4/4095</f>
         <v>13.167619047619048</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="N4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="3">
+        <v>13.167619047619048</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
@@ -711,15 +758,24 @@
       <c r="F5" s="3">
         <v>3413</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="9">
         <f>D5*F5/4095</f>
         <v>11.501684981684981</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="N5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="3">
+        <v>11.501684981684981</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -735,39 +791,60 @@
       <c r="F6" s="3">
         <v>3990</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="9">
         <f>D6*F6/4095</f>
         <v>6.080000000000001</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="N6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="3">
+        <v>6.080000000000001</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="s">
+      <c r="C8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9" t="s">
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9" t="s">
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="9"/>
+      <c r="L8" s="13"/>
+      <c r="N8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.6">
-      <c r="B9" s="9"/>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B9" s="13"/>
       <c r="C9" s="3" t="s">
         <v>1</v>
       </c>
@@ -798,8 +875,24 @@
       <c r="L9" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="N9" s="8"/>
+      <c r="O9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
@@ -836,8 +929,26 @@
       <c r="L10" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="N10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.71519999999999995</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0.28549999999999998</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>255</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
         <v>4</v>
       </c>
@@ -874,8 +985,26 @@
       <c r="L11" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="N11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.1802</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.72729999999999995</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>255</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -912,8 +1041,26 @@
       <c r="L12" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="N12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="P12" s="3">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>255</v>
+      </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
@@ -950,8 +1097,29 @@
       <c r="L13" s="3">
         <v>0.32600000000000001</v>
       </c>
+      <c r="N13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.312</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>167</v>
+      </c>
+      <c r="R13" s="3">
+        <v>190</v>
+      </c>
+      <c r="S13" s="3">
+        <v>255</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
@@ -988,16 +1156,38 @@
       <c r="L14" s="3">
         <v>6.8000000000000005E-2</v>
       </c>
+      <c r="N14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="P14" s="3">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>1</v>
+      </c>
+      <c r="S14" s="3">
+        <v>255</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:G8"/>
+  <mergeCells count="8">
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="H8:J8"/>
+    <mergeCell ref="N3:P3"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:G8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
+++ b/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250410.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_CS1_Echo_Demo\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4CB220-F0E2-4A11-A8AB-3E1971178C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEBB3E9-05AC-4CF7-AE28-9B3BA97664E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="5760" windowWidth="29040" windowHeight="15720" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
   </bookViews>
@@ -317,6 +317,9 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,9 +327,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -682,32 +682,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B3" s="8"/>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="13"/>
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="13"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
@@ -809,27 +809,27 @@
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13" t="s">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="13"/>
+      <c r="L8" s="10"/>
       <c r="N8" s="8" t="s">
         <v>8</v>
       </c>
@@ -844,7 +844,7 @@
       <c r="S8" s="8"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B9" s="13"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="3" t="s">
         <v>1</v>
       </c>
